--- a/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Indirizzo: Ul. Adolfa Waldingera 1a, 31000 Osijek. Distributore/rivenditore di utensili industriali e per manutenzione; rappresentante e importatore per i marchi Elora, Komelon, Scala, Stabila, Picard, Kirschen, Olfa; catalogo di circa 10.000 articoli, negozio fisico ed e-commerce. WebFetch bloccato dal proxy sul dominio; verifica effettuata via WebSearch su sito ufficiale, LinkedIn e directory locali (radno-vrijeme.com).</t>
+          <t>Indirizzo: Ul. Adolfa Waldingera 1a, 31000 Osijek. Distributore/rivenditore di utensili industriali e per manutenzione; rappresentante e importatore per i marchi Elora, Komelon, Scala, Stabila, Picard, Kirschen, Olfa; catalogo di circa 10.000 articoli, negozio fisico ed e-commerce. WebFetch bloccato dal proxy sul dominio; verifica effettuata via WebSearch su sito ufficiale, LinkedIn e directory locali (radno-vrijeme.com). [DUPLICATO — vedi anche: 2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Indirizzo: J. J. Strossmayera 269, 31000 Osijek. Fondata nel 2004, import e distribuzione di utensili professionali e attrezzature; distributore ufficiale saldatrici EWM; centro assistenza autorizzato Makita, Metabo, DeWalt, HiKOKI, Ruko, Weco, Bodor, X-LAS. Email generica confermata da fonti multiple (oltre a webshop@probe.hr, krunoslav@probe.hr). WebFetch bloccato dal proxy; verifica via WebSearch (sito ufficiale, fininfo.hr, companywall.hr, LinkedIn, Instagram).</t>
+          <t>Indirizzo: J. J. Strossmayera 269, 31000 Osijek. Fondata nel 2004, import e distribuzione di utensili professionali e attrezzature; distributore ufficiale saldatrici EWM; centro assistenza autorizzato Makita, Metabo, DeWalt, HiKOKI, Ruko, Weco, Bodor, X-LAS. Email generica confermata da fonti multiple (oltre a webshop@probe.hr, krunoslav@probe.hr). WebFetch bloccato dal proxy; verifica via WebSearch (sito ufficiale, fininfo.hr, companywall.hr, LinkedIn, Instagram). [DUPLICATO — vedi anche: 2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,7 +590,6 @@
           <t>ALATOS d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Josipovac</t>
@@ -613,7 +612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Indirizzo: Matije Gupca 36C, 31220 Josipovac. Societa' attiva dal 10/07/2024 (direttore Kristijan Špoljarić), attivita' registrata G46900 commercio all'ingrosso non specializzato; pagina Facebook 'ALATOS - Profesionalni alati'; specializzata in vendita/distribuzione di utensili (anche Makita) per aziende, artigiani e privati. Confermata su fininfo.hr, companywall.hr, crobiz.net. Il sito web proprio non e' stato individuato/raggiunto (l'URL nella lista grezza era una pagina di directory, non il sito ufficiale) - campo lasciato vuoto. Telefono ed email coerenti su piu' fonti.</t>
+          <t>Indirizzo: Matije Gupca 36C, 31220 Josipovac. Societa' attiva dal 10/07/2024 (direttore Kristijan Špoljarić), attivita' registrata G46900 commercio all'ingrosso non specializzato; pagina Facebook 'ALATOS - Profesionalni alati'; specializzata in vendita/distribuzione di utensili (anche Makita) per aziende, artigiani e privati. Confermata su fininfo.hr, companywall.hr, crobiz.net. Il sito web proprio non e' stato individuato/raggiunto (l'URL nella lista grezza era una pagina di directory, non il sito ufficiale) - campo lasciato vuoto. Telefono ed email coerenti su piu' fonti. [DUPLICATO — vedi anche: 2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-19_19_Croazia_Osjecko-baranjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Filiale di Osijek in Dunavska 71 confermata su Žute Stranice e Waze con lo stesso numero di telefono (+385 31 378 088). Sede legale a Šenkovec/Zagabria. Vendita di cuscinetti, viteria, materiale elettrico e per saldatura, utensili (mole, taglio, elettroutensili) e compressori ABAC. L'email di filiale non è stata confermata in modo indipendente dagli snippet di ricerca (riportata come da lista originale, formato coerente con altre filiali) - da ricontrollare. WebFetch bloccato dal proxy; verifica via WebSearch.</t>
+          <t>Filiale di Osijek in Dunavska 71 confermata su Žute Stranice e Waze con lo stesso numero di telefono (+385 31 378 088). Sede legale a Šenkovec/Zagabria. Vendita di cuscinetti, viteria, materiale elettrico e per saldatura, utensili (mole, taglio, elettroutensili) e compressori ABAC. L'email di filiale non è stata confermata in modo indipendente dagli snippet di ricerca (riportata come da lista originale, formato coerente con altre filiali) - da ricontrollare. WebFetch bloccato dal proxy; verifica via WebSearch. [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
